--- a/api/1/xlsx/fr/AidType.xlsx
+++ b/api/1/xlsx/fr/AidType.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="92">
   <si>
     <t>code</t>
   </si>
@@ -278,6 +278,18 @@
   </si>
   <si>
     <t>Coûts encourus dans d'autres pays fournisseurs non éligibles à l'APD pour l'assistance de base aux demandeurs d'asile et aux réfugiés des pays en développement, jusqu'à 12 mois. Le pays d'accueil et d'origine des réfugiés/demandeurs d'asile doit être précisé dans l'un des champs descriptifs du SNPC (champs 14 ou 19).</t>
+  </si>
+  <si>
+    <t>J01</t>
+  </si>
+  <si>
+    <t>Dons en nature</t>
+  </si>
+  <si>
+    <t>Dons en nature de bien et matériels. Cela comprend l'alimentation, les équipements (dont équipements médicaux) du matériel et les véhicules motorisés.</t>
+  </si>
+  <si>
+    <t>J</t>
   </si>
 </sst>
 </file>
@@ -609,7 +621,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1054,6 +1066,23 @@
         <v>9</v>
       </c>
     </row>
+    <row r="27" spans="1:5">
+      <c r="A27" t="s">
+        <v>88</v>
+      </c>
+      <c r="B27" t="s">
+        <v>89</v>
+      </c>
+      <c r="C27" t="s">
+        <v>90</v>
+      </c>
+      <c r="D27" t="s">
+        <v>91</v>
+      </c>
+      <c r="E27" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
